--- a/Fase 2/Evidencias Grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
+++ b/Fase 2/Evidencias Grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://duoccl0-my.sharepoint.com/personal/ge_galan_profesor_duoc_cl/Documents/2024-2/Clases/CAPSTONE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PARA CORREGIR (2-2025)\CAPSTONE\SEC 2\grupo 2 (Castillo - Cardenas  - Vargas)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="631" documentId="8_{2EFDF332-31E9-4C74-A6B5-E695634C1C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE9E1920-E93E-4291-9C20-328286C7FD32}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0148A9B3-CD09-48FF-9791-CC3F34A0268E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVALUACION2" sheetId="1" r:id="rId1"/>
@@ -45,11 +45,8 @@
     <definedName name="RE_TL">'RELEVANCIA-PUNTAJE'!$B$4</definedName>
     <definedName name="TL">'RELEVANCIA-PUNTAJE'!$B$2</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -61,26 +58,44 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
+  <si>
+    <t>PUNTOS</t>
+  </si>
+  <si>
+    <t>NOTA</t>
+  </si>
   <si>
     <t>INTEGRANTES</t>
   </si>
   <si>
-    <t>GRUPAL</t>
+    <t>Relevancia</t>
   </si>
   <si>
-    <t>Axel Cardenas</t>
+    <t>Puntaje</t>
   </si>
   <si>
-    <t>Diego Castillo</t>
+    <t>Completamente logrado</t>
   </si>
   <si>
-    <t>Diego Vargas</t>
+    <t>Logrado</t>
+  </si>
+  <si>
+    <t>No logrado</t>
+  </si>
+  <si>
+    <t>Muy Relevante</t>
+  </si>
+  <si>
+    <t>GRUPAL</t>
   </si>
   <si>
     <t>Nivel de Logro</t>
@@ -92,25 +107,7 @@
     <t>Aspectos a Evaluar</t>
   </si>
   <si>
-    <t>Completamente logrado</t>
-  </si>
-  <si>
-    <t>Logrado</t>
-  </si>
-  <si>
-    <t>Logro Incipiente</t>
-  </si>
-  <si>
-    <t>No logrado</t>
-  </si>
-  <si>
-    <t>Puntaje</t>
-  </si>
-  <si>
     <t>Nota</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
   <si>
     <t>Indicador de Evaluación</t>
@@ -120,21 +117,6 @@
   </si>
   <si>
     <t>Ponderación del Indicador de Evaluación</t>
-  </si>
-  <si>
-    <r>
-      <t>Completamente Logrado</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  (100%)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -155,6 +137,39 @@
     <t xml:space="preserve">Logro incipiente </t>
   </si>
   <si>
+    <t>El texto presenta de 1 a 5 errores de ortografía, redacción o en las citas y referencias del informe.</t>
+  </si>
+  <si>
+    <t>El texto presenta de 6 a 10 errores de ortografía, redacción o en las citas y referencias del informe.</t>
+  </si>
+  <si>
+    <t>El texto presenta más de 10 errores de ortografía, redacción o en las citas y referencias del informe.</t>
+  </si>
+  <si>
+    <t>El texto cumple con las reglas ortografía y de redacción en todos sus apartados y utiliza correctamente todas las normas de citación y referencias.</t>
+  </si>
+  <si>
+    <t>Logro Incipiente</t>
+  </si>
+  <si>
+    <t>Logro incipiente</t>
+  </si>
+  <si>
+    <r>
+      <t>Completamente Logrado</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  (100%)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">1. Propone ajustes al Proyecto APT considerando dificultades, facilitadores y retroalimentación. </t>
   </si>
   <si>
@@ -173,9 +188,6 @@
     <t>2. Aplica una metodología que permite el logro de los objetivos propuestos, de acuerdo a los estándares de la disciplina.</t>
   </si>
   <si>
-    <t xml:space="preserve">Aplica la metodología definida por el equipo de acuerdo a los estándares de la disciplina, alcanzando los objetivos propuestos para el avance del proyecto. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Aplica la metodología definida de acuerdo a los estándares de la disciplina, pero no se observa el cumplimiento de objetivos propuestos para el avance del proyecto. </t>
   </si>
   <si>
@@ -183,6 +195,27 @@
   </si>
   <si>
     <t xml:space="preserve">Aplica la metodología definida sin cumplir los estándares de la disciplina ni los objetivos propuestos para el avance del proyecto. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </t>
+  </si>
+  <si>
+    <t>8. Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</t>
+  </si>
+  <si>
+    <t>Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</t>
+  </si>
+  <si>
+    <t>Demuestra un trabajo en equipo de manera parcial, en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto, pero no todos participan de manera equitativa de las actividades planificadas en el proyecto</t>
+  </si>
+  <si>
+    <t>Demuestra de manera deficiente el trabajo en equipo en donde los integrantes expresan con poca fluidez y de manera imparcial el conocimiento del tema expuesto y no todos sus miembros participan de manera equitativa de las actividades planificadas en el proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No demuestran un trabajo en equipo, evidenciando en su presentación la nula colaboración de alguno de sus integrantes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplica la metodología definida por el equipo de acuerdo a los estándares de la disciplina, alcanzando los objetivos propuestos para el avance del proyecto. </t>
   </si>
   <si>
     <t>3. Genera evidencias que dan cuenta del avance del Proyecto APT en relación a documentación, programación y almacenamiento de datos , de acuerdo a lo planificado por el equipo y que cumpla con estándares de desarrollo de la industria</t>
@@ -215,21 +248,6 @@
     <t xml:space="preserve">No utiliza lenguaje técnico de su disciplina en los entregables de avance del proyecto. </t>
   </si>
   <si>
-    <t xml:space="preserve">5. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </t>
-  </si>
-  <si>
-    <t>El texto cumple con las reglas ortografía y de redacción en todos sus apartados y utiliza correctamente todas las normas de citación y referencias.</t>
-  </si>
-  <si>
-    <t>El texto presenta de 1 a 5 errores de ortografía, redacción o en las citas y referencias del informe.</t>
-  </si>
-  <si>
-    <t>El texto presenta de 6 a 10 errores de ortografía, redacción o en las citas y referencias del informe.</t>
-  </si>
-  <si>
-    <t>El texto presenta más de 10 errores de ortografía, redacción o en las citas y referencias del informe.</t>
-  </si>
-  <si>
     <t>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estrucutra y nombres solicitados, guardando todas las evidencias de avances en Git</t>
   </si>
   <si>
@@ -260,34 +278,13 @@
     <t>No generan evidencias dentro del repositorio  del proyecto del aporte de cada uno de los integrantes del equipo por lo que no se permite identificar la equidad en el trabajo y la participación de cada estudiante</t>
   </si>
   <si>
-    <t>8. Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</t>
+    <t>Axel Cardenas</t>
   </si>
   <si>
-    <t>Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</t>
+    <t>Diego Castillo</t>
   </si>
   <si>
-    <t>Demuestra un trabajo en equipo de manera parcial, en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto, pero no todos participan de manera equitativa de las actividades planificadas en el proyecto</t>
-  </si>
-  <si>
-    <t>Demuestra de manera deficiente el trabajo en equipo en donde los integrantes expresan con poca fluidez y de manera imparcial el conocimiento del tema expuesto y no todos sus miembros participan de manera equitativa de las actividades planificadas en el proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No demuestran un trabajo en equipo, evidenciando en su presentación la nula colaboración de alguno de sus integrantes. </t>
-  </si>
-  <si>
-    <t>PUNTOS</t>
-  </si>
-  <si>
-    <t>NOTA</t>
-  </si>
-  <si>
-    <t>Relevancia</t>
-  </si>
-  <si>
-    <t>Logro incipiente</t>
-  </si>
-  <si>
-    <t>Muy Relevante</t>
+    <t>Diego Vargas</t>
   </si>
 </sst>
 </file>
@@ -443,7 +440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -576,6 +573,17 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
@@ -763,7 +771,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -791,10 +799,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -812,28 +823,28 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -843,7 +854,7 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -855,40 +866,51 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -897,24 +919,16 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -950,7 +964,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1247,7 +1261,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:K895"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="66.85546875" customWidth="1"/>
@@ -1261,25 +1275,25 @@
     <col min="12" max="24" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="14.45">
+    <row r="2" spans="1:11">
       <c r="C2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.45">
+    <row r="3" spans="1:11">
       <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="14.45">
+        <v>2</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>2</v>
+      <c r="B4" s="25" t="s">
+        <v>62</v>
       </c>
       <c r="C4" s="5">
         <f>EVALUACION2!$C$22</f>
@@ -1287,12 +1301,12 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="14.45">
+    <row r="5" spans="1:11">
       <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>3</v>
+      <c r="B5" s="25" t="s">
+        <v>63</v>
       </c>
       <c r="C5" s="5">
         <f>EVALUACION2!$C$22</f>
@@ -1300,12 +1314,12 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="14.45">
+    <row r="6" spans="1:11">
       <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>4</v>
+      <c r="B6" s="25" t="s">
+        <v>64</v>
       </c>
       <c r="C6" s="5">
         <f>EVALUACION2!$C$22</f>
@@ -1313,438 +1327,434 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="18" outlineLevel="1">
-      <c r="A11" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="41" t="s">
+    <row r="11" spans="1:11" ht="18.75" outlineLevel="1">
+      <c r="A11" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="48"/>
+    </row>
+    <row r="12" spans="1:11" outlineLevel="1">
+      <c r="A12" s="43"/>
+      <c r="B12" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="45"/>
+      <c r="D12" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="E12" s="48"/>
+      <c r="F12" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="54"/>
-    </row>
-    <row r="12" spans="1:11" ht="14.45" outlineLevel="1">
-      <c r="A12" s="55"/>
-      <c r="B12" s="19" t="s">
+      <c r="G12" s="48"/>
+      <c r="H12" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="48"/>
+      <c r="J12" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="54"/>
-      <c r="H12" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="54"/>
-      <c r="J12" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="54"/>
+      <c r="K12" s="48"/>
     </row>
     <row r="13" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="27" t="str">
+      <c r="A13" s="44"/>
+      <c r="B13" s="28" t="str">
         <f>RUBRICA!A4</f>
         <v xml:space="preserve">1. Propone ajustes al Proyecto APT considerando dificultades, facilitadores y retroalimentación. </v>
       </c>
-      <c r="C13" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="14" t="str">
+      <c r="C13" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="15" t="str">
         <f t="shared" ref="D13:D17" si="0">IF($C13=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="15">
         <f>IF(D13="X",100*0.1,"")</f>
         <v>10</v>
       </c>
-      <c r="F13" s="14" t="str">
+      <c r="F13" s="15" t="str">
         <f t="shared" ref="F13:F17" si="1">IF($C13=L,"X","")</f>
         <v/>
       </c>
-      <c r="G13" s="14" t="str">
+      <c r="G13" s="15" t="str">
         <f>IF(F13="X",60*0.1,"")</f>
         <v/>
       </c>
-      <c r="H13" s="14" t="str">
+      <c r="H13" s="15" t="str">
         <f t="shared" ref="H13:H17" si="2">IF($C13=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I13" s="14" t="str">
+      <c r="I13" s="15" t="str">
         <f>IF(H13="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="14" t="str">
+      <c r="J13" s="15" t="str">
         <f t="shared" ref="J13:J17" si="3">IF($C13=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K13" s="14" t="str">
+      <c r="K13" s="15" t="str">
         <f t="shared" ref="K13:K17" si="4">IF($J13="X",0,"")</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:11" ht="26.45" customHeight="1" outlineLevel="1">
-      <c r="A14" s="57"/>
-      <c r="B14" s="27" t="str">
+      <c r="A14" s="44"/>
+      <c r="B14" s="28" t="str">
         <f>RUBRICA!A5</f>
         <v>2. Aplica una metodología que permite el logro de los objetivos propuestos, de acuerdo a los estándares de la disciplina.</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="14" t="str">
+      <c r="C14" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="15" t="str">
         <f t="shared" si="0"/>
         <v>X</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="15">
         <f>IF(D14="X",100*0.1,"")</f>
         <v>10</v>
       </c>
-      <c r="F14" s="14" t="str">
+      <c r="F14" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G14" s="14" t="str">
+      <c r="G14" s="15" t="str">
         <f>IF(F14="X",60*0.1,"")</f>
         <v/>
       </c>
-      <c r="H14" s="14" t="str">
+      <c r="H14" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I14" s="14" t="str">
+      <c r="I14" s="15" t="str">
         <f>IF(H14="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="14" t="str">
+      <c r="J14" s="15" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K14" s="14" t="str">
+      <c r="K14" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="36" outlineLevel="1">
-      <c r="A15" s="57"/>
-      <c r="B15" s="27" t="str">
+    <row r="15" spans="1:11" ht="48" outlineLevel="1">
+      <c r="A15" s="44"/>
+      <c r="B15" s="28" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Genera evidencias que dan cuenta del avance del Proyecto APT en relación a documentación, programación y almacenamiento de datos , de acuerdo a lo planificado por el equipo y que cumpla con estándares de desarrollo de la industria</v>
       </c>
-      <c r="C15" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="14" t="str">
+      <c r="C15" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="15" t="str">
         <f t="shared" si="0"/>
         <v>X</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="15">
         <f>IF(D15="X",100*0.25,"")</f>
         <v>25</v>
       </c>
-      <c r="F15" s="14" t="str">
+      <c r="F15" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G15" s="14" t="str">
+      <c r="G15" s="15" t="str">
         <f>IF(F15="X",60*0.25,"")</f>
         <v/>
       </c>
-      <c r="H15" s="14" t="str">
+      <c r="H15" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I15" s="14" t="str">
+      <c r="I15" s="15" t="str">
         <f>IF(H15="X",30*0.25,"")</f>
         <v/>
       </c>
-      <c r="J15" s="14" t="str">
+      <c r="J15" s="15" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K15" s="14" t="str">
+      <c r="K15" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A16" s="57"/>
-      <c r="B16" s="27" t="str">
+      <c r="A16" s="44"/>
+      <c r="B16" s="28" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Utiliza de manera precisa el lenguaje técnico en los entregables de acuerdo con lo requerido por la disciplina.</v>
       </c>
-      <c r="C16" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="14" t="str">
+      <c r="C16" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="15" t="str">
         <f t="shared" si="0"/>
         <v>X</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="15">
         <f>IF(D16="X",100*0.05,"")</f>
         <v>5</v>
       </c>
-      <c r="F16" s="14" t="str">
+      <c r="F16" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G16" s="14" t="str">
+      <c r="G16" s="15" t="str">
         <f>IF(F16="X",60*0.05,"")</f>
         <v/>
       </c>
-      <c r="H16" s="14" t="str">
+      <c r="H16" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I16" s="14" t="str">
+      <c r="I16" s="15" t="str">
         <f>IF(H16="X",30*0.05,"")</f>
         <v/>
       </c>
-      <c r="J16" s="14" t="str">
+      <c r="J16" s="15" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K16" s="14" t="str">
+      <c r="K16" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A17" s="57"/>
-      <c r="B17" s="27" t="str">
+      <c r="A17" s="44"/>
+      <c r="B17" s="28" t="str">
         <f>RUBRICA!A8</f>
         <v xml:space="preserve">5. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
       </c>
-      <c r="C17" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="14" t="str">
+      <c r="C17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="15" t="str">
         <f t="shared" si="0"/>
         <v>X</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="15">
         <f>IF(D17="X",100*0.05,"")</f>
         <v>5</v>
       </c>
-      <c r="F17" s="14" t="str">
+      <c r="F17" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G17" s="14" t="str">
+      <c r="G17" s="15" t="str">
         <f>IF(F17="X",60*0.05,"")</f>
         <v/>
       </c>
-      <c r="H17" s="14" t="str">
+      <c r="H17" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I17" s="14" t="str">
+      <c r="I17" s="15" t="str">
         <f>IF(H17="X",30*0.05,"")</f>
         <v/>
       </c>
-      <c r="J17" s="14" t="str">
+      <c r="J17" s="15" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K17" s="14" t="str">
+      <c r="K17" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A18" s="57"/>
-      <c r="B18" s="27" t="str">
+    <row r="18" spans="1:11" ht="36" outlineLevel="1">
+      <c r="A18" s="44"/>
+      <c r="B18" s="28" t="str">
         <f>RUBRICA!A9</f>
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estrucutra y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
-      <c r="C18" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="14" t="str">
+      <c r="C18" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="15" t="str">
         <f>IF($C18=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="15">
         <f>IF(D18="X",100*0.2,"")</f>
         <v>20</v>
       </c>
-      <c r="F18" s="14" t="str">
+      <c r="F18" s="15" t="str">
         <f>IF($C18=L,"X","")</f>
         <v/>
       </c>
-      <c r="G18" s="14" t="str">
+      <c r="G18" s="15" t="str">
         <f>IF(F18="X",60*0.2,"")</f>
         <v/>
       </c>
-      <c r="H18" s="14" t="str">
+      <c r="H18" s="15" t="str">
         <f>IF($C18=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I18" s="14" t="str">
+      <c r="I18" s="15" t="str">
         <f>IF(H18="X",30*0.2,"")</f>
         <v/>
       </c>
-      <c r="J18" s="14" t="str">
+      <c r="J18" s="15" t="str">
         <f>IF($C18=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K18" s="14" t="str">
+      <c r="K18" s="15" t="str">
         <f t="shared" ref="K18:K20" si="5">IF($J18="X",0,"")</f>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:11" ht="36" outlineLevel="1">
-      <c r="A19" s="57"/>
-      <c r="B19" s="27" t="str">
+      <c r="A19" s="44"/>
+      <c r="B19" s="28" t="str">
         <f>RUBRICA!A10</f>
         <v>7.- Generan evidencias claras dentro del repositorio  del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante.</v>
       </c>
-      <c r="C19" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="14" t="str">
+      <c r="C19" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="15" t="str">
         <f>IF($C19=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="15">
         <f>IF(D19="X",100*0.15,"")</f>
         <v>15</v>
       </c>
-      <c r="F19" s="14" t="str">
+      <c r="F19" s="15" t="str">
         <f>IF($C19=L,"X","")</f>
         <v/>
       </c>
-      <c r="G19" s="14" t="str">
+      <c r="G19" s="15" t="str">
         <f>IF(F19="X",60*0.15,"")</f>
         <v/>
       </c>
-      <c r="H19" s="14" t="str">
+      <c r="H19" s="15" t="str">
         <f>IF($C19=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I19" s="14" t="str">
+      <c r="I19" s="15" t="str">
         <f>IF(H19="X",30*0.15,"")</f>
         <v/>
       </c>
-      <c r="J19" s="14" t="str">
+      <c r="J19" s="15" t="str">
         <f>IF($C19=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K19" s="14" t="str">
+      <c r="K19" s="15" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:11" ht="36" outlineLevel="1">
-      <c r="A20" s="57"/>
-      <c r="B20" s="27" t="str">
+      <c r="A20" s="44"/>
+      <c r="B20" s="28" t="str">
         <f>RUBRICA!A11</f>
         <v>8. Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="14" t="str">
+      <c r="C20" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="15" t="str">
         <f>IF($C20=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="15">
         <f>IF(D20="X",100*0.1,"")</f>
         <v>10</v>
       </c>
-      <c r="F20" s="14" t="str">
+      <c r="F20" s="15" t="str">
         <f>IF($C20=L,"X","")</f>
         <v/>
       </c>
-      <c r="G20" s="14" t="str">
+      <c r="G20" s="15" t="str">
         <f>IF(F20="X",60*0.1,"")</f>
         <v/>
       </c>
-      <c r="H20" s="14" t="str">
+      <c r="H20" s="15" t="str">
         <f>IF($C20=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I20" s="14" t="str">
+      <c r="I20" s="15" t="str">
         <f>IF(H20="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="14" t="str">
+      <c r="J20" s="15" t="str">
         <f>IF($C20=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K20" s="14" t="str">
+      <c r="K20" s="15" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A21" s="55"/>
-      <c r="B21" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="30">
+      <c r="A21" s="43"/>
+      <c r="B21" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="31">
         <f>E21+G21+I21+K21</f>
         <v>100</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15">
+      <c r="D21" s="16"/>
+      <c r="E21" s="16">
         <f>SUM(E13:E20)</f>
         <v>100</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15">
+      <c r="F21" s="16"/>
+      <c r="G21" s="16">
         <f>SUM(G13:G20)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15">
+      <c r="H21" s="16"/>
+      <c r="I21" s="16">
         <f>SUM(I13:I20)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15">
+      <c r="J21" s="16"/>
+      <c r="K21" s="16">
         <f>SUM(K13:K20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A22" s="56"/>
-      <c r="B22" s="29" t="s">
+      <c r="A22" s="45"/>
+      <c r="B22" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <f>VLOOKUP(C21,ESCALA_IEP!A2:B202,2,FALSE)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1">
-      <c r="D23" t="s">
-        <v>14</v>
-      </c>
-    </row>
+    <row r="23" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="24" spans="1:11" ht="48" customHeight="1">
-      <c r="B24" s="33"/>
+      <c r="B24" s="34"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
     </row>
     <row r="26" spans="1:11" ht="31.15" customHeight="1">
-      <c r="B26" s="34"/>
+      <c r="B26" s="35"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="28" spans="1:11" ht="15.75" customHeight="1"/>
@@ -2659,210 +2669,210 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B396D1B-8A63-4A90-BA20-D34AC13A3962}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A1" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="44" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="52"/>
+      <c r="B2" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="57" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="45"/>
-      <c r="B2" s="50" t="s">
+      <c r="D2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="E2" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="52"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A3" s="52"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="37">
+        <v>-0.3</v>
+      </c>
+      <c r="E3" s="37">
+        <v>0</v>
+      </c>
+      <c r="F3" s="56"/>
+    </row>
+    <row r="4" spans="1:6" ht="51.75" thickBot="1">
+      <c r="A4" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="51.75" thickBot="1">
+      <c r="A5" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="90" thickBot="1">
+      <c r="A6" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="39" thickBot="1">
+      <c r="A7" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="51">
+      <c r="A8" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="45"/>
-    </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="36">
-        <v>-0.3</v>
-      </c>
-      <c r="E3" s="36">
-        <v>0</v>
-      </c>
-      <c r="F3" s="49"/>
-    </row>
-    <row r="4" spans="1:6" ht="55.9" thickBot="1">
-      <c r="A4" s="23" t="s">
+      <c r="E8" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="55.9" thickBot="1">
-      <c r="A5" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="97.15" thickBot="1">
-      <c r="A6" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="22">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="42" thickBot="1">
-      <c r="A7" s="23" t="s">
+      <c r="F8" s="38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="51.75" thickBot="1">
+      <c r="A9" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="64.5" thickBot="1">
+      <c r="A10" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="32">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="81.599999999999994" customHeight="1">
+      <c r="A11" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C11" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E11" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="55.15">
-      <c r="A8" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="55.9" thickBot="1">
-      <c r="A9" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="22">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="69.599999999999994" thickBot="1">
-      <c r="A10" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="31">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="81.599999999999994" customHeight="1">
-      <c r="A11" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="35">
+      <c r="F11" s="36">
         <v>10</v>
       </c>
     </row>
@@ -2881,20 +2891,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.45">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2902,7 +2912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.45">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>0.5</v>
       </c>
@@ -2910,7 +2920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.45">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2918,7 +2928,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.45">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>1.5</v>
       </c>
@@ -2926,7 +2936,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.45">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -2934,7 +2944,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.45">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>2.5</v>
       </c>
@@ -2942,7 +2952,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.45">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>3</v>
       </c>
@@ -2950,7 +2960,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>3.5</v>
       </c>
@@ -2958,7 +2968,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.45">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>4</v>
       </c>
@@ -2966,7 +2976,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.45">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>4.5</v>
       </c>
@@ -2974,7 +2984,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.45">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>5</v>
       </c>
@@ -2982,7 +2992,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.45">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>5.5</v>
       </c>
@@ -2990,7 +3000,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.45">
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>6</v>
       </c>
@@ -2998,7 +3008,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.45">
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>6.5</v>
       </c>
@@ -3006,7 +3016,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.45">
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>7</v>
       </c>
@@ -3014,7 +3024,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.45">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>7.5</v>
       </c>
@@ -3022,7 +3032,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.45">
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>8</v>
       </c>
@@ -3030,7 +3040,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.45">
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>8.5</v>
       </c>
@@ -3038,7 +3048,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.45">
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>9</v>
       </c>
@@ -5309,20 +5319,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="14.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5330,7 +5340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.45">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5338,7 +5348,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.45">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5346,7 +5356,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.45">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5354,7 +5364,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.45">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5362,7 +5372,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.45">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5370,7 +5380,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.45">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5378,7 +5388,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5386,7 +5396,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.45">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5394,7 +5404,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.45">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5402,7 +5412,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.45">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5410,7 +5420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.45">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5418,7 +5428,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.45">
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5426,7 +5436,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.45">
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5434,7 +5444,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.45">
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5442,7 +5452,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.45">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5450,7 +5460,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.45">
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5458,7 +5468,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.45">
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5466,7 +5476,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.45">
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -6701,20 +6711,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.45">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6722,7 +6732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.45">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>0.5</v>
       </c>
@@ -6730,7 +6740,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.45">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6738,7 +6748,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.45">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>1.5</v>
       </c>
@@ -6746,7 +6756,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.45">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -6754,7 +6764,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.45">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>2.5</v>
       </c>
@@ -6762,7 +6772,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.45">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>3</v>
       </c>
@@ -6770,7 +6780,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>3.5</v>
       </c>
@@ -6778,7 +6788,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.45">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>4</v>
       </c>
@@ -6786,7 +6796,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.45">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>4.5</v>
       </c>
@@ -6794,7 +6804,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.45">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>5</v>
       </c>
@@ -6802,7 +6812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.45">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>5.5</v>
       </c>
@@ -6810,7 +6820,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.45">
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>6</v>
       </c>
@@ -6818,7 +6828,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.45">
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>6.5</v>
       </c>
@@ -6826,7 +6836,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.45">
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>7</v>
       </c>
@@ -6834,7 +6844,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.45">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>7.5</v>
       </c>
@@ -6842,7 +6852,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.45">
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>8</v>
       </c>
@@ -6850,7 +6860,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.45">
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>8.5</v>
       </c>
@@ -6858,7 +6868,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.45">
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>9</v>
       </c>
@@ -8083,67 +8093,67 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="25" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45">
-      <c r="A1" s="52" t="s">
-        <v>63</v>
+    <row r="1" spans="1:5">
+      <c r="A1" s="59" t="s">
+        <v>3</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" ht="43.9" thickBot="1">
-      <c r="A2" s="58"/>
+    <row r="2" spans="1:5" ht="45.75" thickBot="1">
+      <c r="A2" s="60"/>
       <c r="B2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30.75" thickBot="1">
+      <c r="A3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="29.45" thickBot="1">
-      <c r="A3" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="12">
+      <c r="B3" s="13">
         <v>4</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="13">
         <v>3</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="13">
         <v>2</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" thickBot="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-    </row>
-    <row r="5" spans="1:5" thickBot="1">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
